--- a/export.xlsx
+++ b/export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac63d6fe77ee4271/Plocha/pt excely/kontrola_produktu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{EC444B58-81F2-484C-9A0C-18A987A0DB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C03E9ACF-1E61-4F83-8DF9-B86AA298F088}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{EC444B58-81F2-484C-9A0C-18A987A0DB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59BC04F5-CB6A-43D5-A249-ED96ACBFC650}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{A2E7916D-1111-4B7D-B9BD-08E201C91CE7}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="693">
   <si>
     <t>ID</t>
   </si>
@@ -2579,104 +2579,7 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="16">
-          <cell r="B16"/>
-          <cell r="D16"/>
-          <cell r="F16"/>
-          <cell r="H16"/>
-          <cell r="J16"/>
-          <cell r="L16"/>
-          <cell r="N16"/>
-          <cell r="P16"/>
-          <cell r="R16"/>
-          <cell r="T16"/>
-        </row>
-        <row r="17">
-          <cell r="B17"/>
-          <cell r="D17"/>
-          <cell r="F17"/>
-          <cell r="H17"/>
-          <cell r="J17"/>
-          <cell r="L17"/>
-          <cell r="N17"/>
-          <cell r="P17"/>
-          <cell r="R17"/>
-          <cell r="T17"/>
-        </row>
-        <row r="18">
-          <cell r="B18"/>
-          <cell r="D18"/>
-          <cell r="F18"/>
-          <cell r="H18"/>
-          <cell r="J18"/>
-          <cell r="L18"/>
-          <cell r="N18"/>
-          <cell r="P18"/>
-          <cell r="R18"/>
-          <cell r="T18"/>
-        </row>
-        <row r="19">
-          <cell r="B19"/>
-          <cell r="D19"/>
-          <cell r="F19"/>
-          <cell r="H19"/>
-          <cell r="J19"/>
-          <cell r="L19"/>
-          <cell r="N19"/>
-          <cell r="P19"/>
-          <cell r="R19"/>
-          <cell r="T19"/>
-        </row>
-        <row r="20">
-          <cell r="B20"/>
-          <cell r="D20"/>
-          <cell r="F20"/>
-          <cell r="H20"/>
-          <cell r="J20"/>
-          <cell r="L20"/>
-          <cell r="N20"/>
-          <cell r="P20"/>
-          <cell r="R20"/>
-          <cell r="T20"/>
-        </row>
-        <row r="21">
-          <cell r="B21"/>
-          <cell r="D21"/>
-          <cell r="F21"/>
-          <cell r="H21"/>
-          <cell r="J21"/>
-          <cell r="L21"/>
-          <cell r="N21"/>
-          <cell r="P21"/>
-          <cell r="R21"/>
-          <cell r="T21"/>
-        </row>
-        <row r="22">
-          <cell r="B22"/>
-          <cell r="D22"/>
-          <cell r="F22"/>
-          <cell r="H22"/>
-          <cell r="J22"/>
-          <cell r="L22"/>
-          <cell r="N22"/>
-          <cell r="P22"/>
-          <cell r="R22"/>
-          <cell r="T22"/>
-        </row>
-        <row r="23">
-          <cell r="B23"/>
-          <cell r="D23"/>
-          <cell r="F23"/>
-          <cell r="H23"/>
-          <cell r="J23"/>
-          <cell r="L23"/>
-          <cell r="N23"/>
-          <cell r="P23"/>
-          <cell r="R23"/>
-          <cell r="T23"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
@@ -8501,8 +8404,8 @@
       </c>
       <c r="J61" s="15"/>
       <c r="K61" s="14"/>
-      <c r="L61" s="19" t="s">
-        <v>196</v>
+      <c r="L61" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="M61" s="14">
         <v>20</v>
@@ -8591,8 +8494,8 @@
       <c r="K62" s="11">
         <v>85</v>
       </c>
-      <c r="L62" s="15" t="s">
-        <v>74</v>
+      <c r="L62" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="M62" s="11">
         <v>5</v>
@@ -8672,7 +8575,7 @@
         <v>85</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M63" s="11">
         <v>5</v>
@@ -8752,7 +8655,7 @@
         <v>85</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="M64" s="11">
         <v>5</v>
@@ -8827,8 +8730,8 @@
       </c>
       <c r="J65" s="23"/>
       <c r="K65" s="6"/>
-      <c r="L65" s="1" t="s">
-        <v>170</v>
+      <c r="L65" s="23" t="s">
+        <v>82</v>
       </c>
       <c r="M65" s="6">
         <v>25</v>
@@ -8911,8 +8814,8 @@
       </c>
       <c r="J66" s="15"/>
       <c r="K66" s="14"/>
-      <c r="L66" s="23" t="s">
-        <v>82</v>
+      <c r="L66" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="M66" s="14">
         <v>20</v>
@@ -9010,7 +8913,7 @@
         <v>30</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M67" s="14">
         <v>40</v>
@@ -9105,7 +9008,7 @@
         <v>30</v>
       </c>
       <c r="L68" s="15" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="M68" s="14">
         <v>30</v>
@@ -9210,7 +9113,7 @@
         <v>30</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="M69" s="15">
         <v>30</v>
@@ -9403,8 +9306,8 @@
       <c r="K71" s="34">
         <v>25</v>
       </c>
-      <c r="L71" s="15" t="s">
-        <v>98</v>
+      <c r="L71" s="29" t="s">
+        <v>216</v>
       </c>
       <c r="M71" s="34">
         <v>5</v>
@@ -9485,8 +9388,8 @@
       <c r="I72" s="38"/>
       <c r="J72" s="7"/>
       <c r="K72" s="39"/>
-      <c r="L72" s="29" t="s">
-        <v>216</v>
+      <c r="L72" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="M72" s="7">
         <v>40</v>
@@ -9581,9 +9484,6 @@
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="11"/>
-      <c r="L73" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="M73" s="11"/>
       <c r="N73" s="1"/>
       <c r="O73" s="11"/>
